--- a/planificacion.xlsx
+++ b/planificacion.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://eebmanresa-my.sharepoint.com/personal/daniel_castro_eebmanresa_org/Documents/CALENDARI/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://eebmanresa-my.sharepoint.com/personal/daniel_castro_eebmanresa_org/Documents/CALENDARI/APP ORG CULTE/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{653B12E3-F56A-4EEC-AEB5-53D8FD942236}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="5" documentId="8_{653B12E3-F56A-4EEC-AEB5-53D8FD942236}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3ECD6689-53CD-45D2-8F4C-06EE31EBF2C6}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Resumen Culto" sheetId="1" r:id="rId1"/>
@@ -35,13 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="96" uniqueCount="59">
-  <si>
-    <t>Informe y Resumen del Servicio Dominical</t>
-  </si>
-  <si>
-    <t>Vista ejecutiva y consultable por fecha</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="95" uniqueCount="58">
   <si>
     <t>Seleccionar Fecha del Culto:</t>
   </si>
@@ -97,12 +91,6 @@
     <t>Ofrenda (2)</t>
   </si>
   <si>
-    <t>Gestión de Servicios Dominicales — Iglesia Bautista</t>
-  </si>
-  <si>
-    <t>Organización general de voluntarios por culto</t>
-  </si>
-  <si>
     <t>Fecha</t>
   </si>
   <si>
@@ -212,6 +200,15 @@
   </si>
   <si>
     <t>Rosa Carrasco</t>
+  </si>
+  <si>
+    <t>ORG CULTES - EEBM</t>
+  </si>
+  <si>
+    <t>Organització de servei al culte</t>
+  </si>
+  <si>
+    <t>RESUM ORG CULTE</t>
   </si>
 </sst>
 </file>
@@ -408,16 +405,16 @@
     <xf numFmtId="0" fontId="5" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="14" fontId="6" fillId="5" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -731,19 +728,17 @@
   <sheetData>
     <row r="2" spans="2:4" ht="20.25" x14ac:dyDescent="0.3">
       <c r="B2" s="1" t="s">
-        <v>0</v>
+        <v>57</v>
       </c>
     </row>
     <row r="3" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B3" s="2" t="s">
-        <v>1</v>
-      </c>
+      <c r="B3" s="2"/>
     </row>
     <row r="5" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B5" s="12" t="s">
-        <v>2</v>
-      </c>
-      <c r="C5" s="19">
+        <v>0</v>
+      </c>
+      <c r="C5" s="17">
         <f>Planificación!A5</f>
         <v>46264</v>
       </c>
@@ -753,14 +748,14 @@
       </c>
     </row>
     <row r="8" spans="2:4" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B8" s="16" t="s">
-        <v>3</v>
-      </c>
-      <c r="C8" s="17"/>
+      <c r="B8" s="18" t="s">
+        <v>1</v>
+      </c>
+      <c r="C8" s="19"/>
     </row>
     <row r="9" spans="2:4" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B9" s="14" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C9" s="15" t="str">
         <f>VLOOKUP(C5, Planificación!A5:P25, 3, FALSE)</f>
@@ -769,7 +764,7 @@
     </row>
     <row r="10" spans="2:4" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B10" s="14" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C10" s="15" t="str">
         <f>VLOOKUP(C5, Planificación!A5:P25, 4, FALSE)</f>
@@ -778,7 +773,7 @@
     </row>
     <row r="11" spans="2:4" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B11" s="14" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="C11" s="15" t="str">
         <f>VLOOKUP(C5, Planificación!A5:P25, 5, FALSE)</f>
@@ -787,7 +782,7 @@
     </row>
     <row r="12" spans="2:4" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B12" s="14" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C12" s="15" t="str">
         <f>VLOOKUP(C5, Planificación!A5:P25, 6, FALSE)</f>
@@ -795,14 +790,14 @@
       </c>
     </row>
     <row r="14" spans="2:4" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B14" s="16" t="s">
-        <v>8</v>
-      </c>
-      <c r="C14" s="17"/>
+      <c r="B14" s="18" t="s">
+        <v>6</v>
+      </c>
+      <c r="C14" s="19"/>
     </row>
     <row r="15" spans="2:4" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B15" s="14" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C15" s="15" t="str">
         <f>VLOOKUP(C5, Planificación!A5:P25, 7, FALSE)</f>
@@ -811,7 +806,7 @@
     </row>
     <row r="16" spans="2:4" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B16" s="14" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C16" s="15" t="str">
         <f>VLOOKUP(C5, Planificación!A5:P25, 8, FALSE)</f>
@@ -819,14 +814,14 @@
       </c>
     </row>
     <row r="18" spans="2:3" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B18" s="16" t="s">
-        <v>11</v>
-      </c>
-      <c r="C18" s="17"/>
+      <c r="B18" s="18" t="s">
+        <v>9</v>
+      </c>
+      <c r="C18" s="19"/>
     </row>
     <row r="19" spans="2:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B19" s="14" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C19" s="15" t="str">
         <f>VLOOKUP(C5, Planificación!A5:P25, 9, FALSE)</f>
@@ -835,7 +830,7 @@
     </row>
     <row r="20" spans="2:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B20" s="14" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C20" s="15" t="str">
         <f>VLOOKUP(C5, Planificación!A5:P25, 10, FALSE)</f>
@@ -844,7 +839,7 @@
     </row>
     <row r="21" spans="2:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B21" s="14" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="C21" s="15" t="str">
         <f>VLOOKUP(C5, Planificación!A5:P25, 11, FALSE)</f>
@@ -852,14 +847,14 @@
       </c>
     </row>
     <row r="23" spans="2:3" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B23" s="16" t="s">
-        <v>35</v>
-      </c>
-      <c r="C23" s="17"/>
+      <c r="B23" s="18" t="s">
+        <v>31</v>
+      </c>
+      <c r="C23" s="19"/>
     </row>
     <row r="24" spans="2:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B24" s="14" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C24" s="15">
         <f>VLOOKUP(C5, Planificación!A5:P25, 12, FALSE)</f>
@@ -868,7 +863,7 @@
     </row>
     <row r="25" spans="2:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B25" s="14" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="C25" s="15">
         <f>VLOOKUP(C5, Planificación!A5:P25, 13, FALSE)</f>
@@ -877,7 +872,7 @@
     </row>
     <row r="26" spans="2:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B26" s="14" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="C26" s="15">
         <f>VLOOKUP(C5, Planificación!A5:P25, 14, FALSE)</f>
@@ -886,7 +881,7 @@
     </row>
     <row r="27" spans="2:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B27" s="14" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="C27" s="15" t="str">
         <f>VLOOKUP(C5, Planificación!A5:P25, 15, FALSE)</f>
@@ -895,7 +890,7 @@
     </row>
     <row r="28" spans="2:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B28" s="14" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="C28" s="15" t="str">
         <f>VLOOKUP(C5, Planificación!A5:P25, 16, FALSE)</f>
@@ -925,62 +920,62 @@
   <sheetData>
     <row r="1" spans="1:16" ht="20.25" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
-        <v>20</v>
+        <v>55</v>
       </c>
     </row>
     <row r="2" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>21</v>
+        <v>56</v>
       </c>
     </row>
     <row r="4" spans="1:16" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="D4" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E4" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F4" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G4" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="H4" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I4" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="J4" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="K4" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="L4" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="M4" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="B4" s="3" t="s">
+      <c r="N4" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="C4" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="D4" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="E4" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="F4" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="G4" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="H4" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="I4" s="3" t="s">
+      <c r="O4" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="J4" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="K4" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="L4" s="3" t="s">
+      <c r="P4" s="3" t="s">
         <v>25</v>
-      </c>
-      <c r="M4" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="N4" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="O4" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="P4" s="3" t="s">
-        <v>29</v>
       </c>
     </row>
     <row r="5" spans="1:16" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -988,49 +983,47 @@
         <v>46264</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="C5" s="6" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="D5" s="6" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="E5" s="6" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="F5" s="6" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="G5" s="6" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="H5" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="I5" s="6" t="s">
         <v>45</v>
       </c>
-      <c r="I5" s="6" t="s">
+      <c r="J5" s="6" t="s">
         <v>49</v>
       </c>
-      <c r="J5" s="6" t="s">
-        <v>53</v>
-      </c>
       <c r="K5" s="6" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="L5" s="8"/>
       <c r="M5" s="9"/>
       <c r="N5" s="9"/>
       <c r="O5" s="8" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="P5" s="9" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
     </row>
     <row r="6" spans="1:16" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="7">
-        <v>46271</v>
-      </c>
+      <c r="A6" s="7"/>
       <c r="B6" s="8"/>
       <c r="C6" s="9"/>
       <c r="D6" s="9"/>
@@ -1048,9 +1041,7 @@
       <c r="P6" s="6"/>
     </row>
     <row r="7" spans="1:16" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="4">
-        <v>46278</v>
-      </c>
+      <c r="A7" s="4"/>
       <c r="B7" s="5"/>
       <c r="C7" s="6"/>
       <c r="D7" s="6"/>
@@ -1068,9 +1059,7 @@
       <c r="P7" s="9"/>
     </row>
     <row r="8" spans="1:16" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="7">
-        <v>46285</v>
-      </c>
+      <c r="A8" s="7"/>
       <c r="B8" s="8"/>
       <c r="C8" s="9"/>
       <c r="D8" s="9"/>
@@ -1088,9 +1077,7 @@
       <c r="P8" s="6"/>
     </row>
     <row r="9" spans="1:16" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="4">
-        <v>46292</v>
-      </c>
+      <c r="A9" s="4"/>
       <c r="B9" s="5"/>
       <c r="C9" s="6"/>
       <c r="D9" s="6"/>
@@ -1108,9 +1095,7 @@
       <c r="P9" s="9"/>
     </row>
     <row r="10" spans="1:16" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="7">
-        <v>46299</v>
-      </c>
+      <c r="A10" s="7"/>
       <c r="B10" s="8"/>
       <c r="C10" s="9"/>
       <c r="D10" s="9"/>
@@ -1128,9 +1113,7 @@
       <c r="P10" s="6"/>
     </row>
     <row r="11" spans="1:16" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="4">
-        <v>46306</v>
-      </c>
+      <c r="A11" s="4"/>
       <c r="B11" s="5"/>
       <c r="C11" s="6"/>
       <c r="D11" s="6"/>
@@ -1148,9 +1131,7 @@
       <c r="P11" s="9"/>
     </row>
     <row r="12" spans="1:16" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="7">
-        <v>46313</v>
-      </c>
+      <c r="A12" s="7"/>
       <c r="B12" s="8"/>
       <c r="C12" s="9"/>
       <c r="D12" s="9"/>
@@ -1168,9 +1149,7 @@
       <c r="P12" s="9"/>
     </row>
     <row r="13" spans="1:16" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="4">
-        <v>46320</v>
-      </c>
+      <c r="A13" s="4"/>
       <c r="B13" s="5"/>
       <c r="C13" s="6"/>
       <c r="D13" s="6"/>
@@ -1188,9 +1167,7 @@
       <c r="P13" s="6"/>
     </row>
     <row r="14" spans="1:16" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="4">
-        <v>46327</v>
-      </c>
+      <c r="A14" s="4"/>
       <c r="B14" s="5"/>
       <c r="C14" s="6"/>
       <c r="D14" s="6"/>
@@ -1208,9 +1185,7 @@
       <c r="P14" s="9"/>
     </row>
     <row r="15" spans="1:16" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="7">
-        <v>46334</v>
-      </c>
+      <c r="A15" s="7"/>
       <c r="B15" s="8"/>
       <c r="C15" s="9"/>
       <c r="D15" s="9"/>
@@ -1228,9 +1203,7 @@
       <c r="P15" s="6"/>
     </row>
     <row r="16" spans="1:16" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="4">
-        <v>46341</v>
-      </c>
+      <c r="A16" s="4"/>
       <c r="B16" s="5"/>
       <c r="C16" s="6"/>
       <c r="D16" s="6"/>
@@ -1248,9 +1221,7 @@
       <c r="P16" s="9"/>
     </row>
     <row r="17" spans="1:16" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="7">
-        <v>46348</v>
-      </c>
+      <c r="A17" s="7"/>
       <c r="B17" s="8"/>
       <c r="C17" s="9"/>
       <c r="D17" s="9"/>
@@ -1268,9 +1239,7 @@
       <c r="P17" s="6"/>
     </row>
     <row r="18" spans="1:16" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="4">
-        <v>46355</v>
-      </c>
+      <c r="A18" s="4"/>
       <c r="B18" s="5"/>
       <c r="C18" s="6"/>
       <c r="D18" s="6"/>
@@ -1288,9 +1257,7 @@
       <c r="P18" s="9"/>
     </row>
     <row r="19" spans="1:16" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="7">
-        <v>46362</v>
-      </c>
+      <c r="A19" s="7"/>
       <c r="B19" s="8"/>
       <c r="C19" s="9"/>
       <c r="D19" s="9"/>
@@ -1308,9 +1275,7 @@
       <c r="P19" s="9"/>
     </row>
     <row r="20" spans="1:16" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="4">
-        <v>46369</v>
-      </c>
+      <c r="A20" s="4"/>
       <c r="B20" s="5"/>
       <c r="C20" s="6"/>
       <c r="D20" s="6"/>
@@ -1328,9 +1293,7 @@
       <c r="P20" s="6"/>
     </row>
     <row r="21" spans="1:16" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="7">
-        <v>46376</v>
-      </c>
+      <c r="A21" s="7"/>
       <c r="B21" s="8"/>
       <c r="C21" s="9"/>
       <c r="D21" s="9"/>
@@ -1348,9 +1311,7 @@
       <c r="P21" s="9"/>
     </row>
     <row r="22" spans="1:16" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="4">
-        <v>46383</v>
-      </c>
+      <c r="A22" s="4"/>
       <c r="B22" s="5"/>
       <c r="C22" s="6"/>
       <c r="D22" s="6"/>
@@ -1368,9 +1329,7 @@
       <c r="P22" s="6"/>
     </row>
     <row r="23" spans="1:16" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="4">
-        <v>46390</v>
-      </c>
+      <c r="A23" s="4"/>
       <c r="B23" s="5"/>
       <c r="C23" s="6"/>
       <c r="D23" s="6"/>
@@ -1388,9 +1347,7 @@
       <c r="P23" s="9"/>
     </row>
     <row r="24" spans="1:16" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="7">
-        <v>46397</v>
-      </c>
+      <c r="A24" s="7"/>
       <c r="B24" s="8"/>
       <c r="C24" s="9"/>
       <c r="D24" s="9"/>
@@ -1408,9 +1365,7 @@
       <c r="P24" s="7"/>
     </row>
     <row r="25" spans="1:16" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="4">
-        <v>46404</v>
-      </c>
+      <c r="A25" s="4"/>
       <c r="B25" s="5"/>
       <c r="C25" s="6"/>
       <c r="D25" s="6"/>
@@ -1428,9 +1383,7 @@
       <c r="P25" s="4"/>
     </row>
     <row r="26" spans="1:16" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="7">
-        <v>46411</v>
-      </c>
+      <c r="A26" s="7"/>
       <c r="B26" s="8"/>
       <c r="C26" s="9"/>
       <c r="D26" s="9"/>
@@ -1448,9 +1401,7 @@
       <c r="P26" s="7"/>
     </row>
     <row r="27" spans="1:16" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="4">
-        <v>46418</v>
-      </c>
+      <c r="A27" s="4"/>
       <c r="B27" s="5"/>
       <c r="C27" s="6"/>
       <c r="D27" s="6"/>
@@ -1468,9 +1419,7 @@
       <c r="P27" s="4"/>
     </row>
     <row r="28" spans="1:16" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="7">
-        <v>46425</v>
-      </c>
+      <c r="A28" s="7"/>
       <c r="B28" s="8"/>
       <c r="C28" s="9"/>
       <c r="D28" s="9"/>
@@ -1488,9 +1437,7 @@
       <c r="P28" s="7"/>
     </row>
     <row r="29" spans="1:16" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="4">
-        <v>46432</v>
-      </c>
+      <c r="A29" s="4"/>
       <c r="B29" s="5"/>
       <c r="C29" s="6"/>
       <c r="D29" s="6"/>
@@ -1603,156 +1550,156 @@
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1" s="10" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="B1" s="10" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="C1" s="10" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D1" s="10" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E1" s="10" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="F1" s="10" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="G1" s="10" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="H1" s="10" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="I1" s="10" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A2" s="11" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="B2" s="11" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="C2" s="11" t="s">
+        <v>41</v>
+      </c>
+      <c r="D2" s="11" t="s">
+        <v>41</v>
+      </c>
+      <c r="E2" s="11" t="s">
         <v>45</v>
       </c>
-      <c r="D2" s="11" t="s">
-        <v>45</v>
-      </c>
-      <c r="E2" s="11" t="s">
-        <v>49</v>
-      </c>
       <c r="F2" s="11" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="G2" s="11" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="H2" s="11" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="I2" s="11" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A3" s="11" t="s">
+        <v>33</v>
+      </c>
+      <c r="B3" s="11" t="s">
+        <v>39</v>
+      </c>
+      <c r="C3" s="11" t="s">
+        <v>42</v>
+      </c>
+      <c r="D3" s="11" t="s">
+        <v>42</v>
+      </c>
+      <c r="E3" s="11" t="s">
+        <v>47</v>
+      </c>
+      <c r="F3" s="11" t="s">
+        <v>49</v>
+      </c>
+      <c r="G3" s="11" t="s">
+        <v>50</v>
+      </c>
+      <c r="H3" s="11" t="s">
         <v>37</v>
       </c>
-      <c r="B3" s="11" t="s">
-        <v>43</v>
-      </c>
-      <c r="C3" s="11" t="s">
-        <v>46</v>
-      </c>
-      <c r="D3" s="11" t="s">
-        <v>46</v>
-      </c>
-      <c r="E3" s="11" t="s">
-        <v>51</v>
-      </c>
-      <c r="F3" s="11" t="s">
-        <v>53</v>
-      </c>
-      <c r="G3" s="11" t="s">
-        <v>54</v>
-      </c>
-      <c r="H3" s="11" t="s">
-        <v>41</v>
-      </c>
       <c r="I3" s="11" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A4" s="11" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="B4" s="11" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="C4" s="11" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="D4" s="11" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="E4" s="11" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="H4" s="11" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="I4" s="11" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A5" s="11" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="B5" s="11" t="s">
-        <v>56</v>
-      </c>
-      <c r="C5" s="18" t="s">
-        <v>48</v>
+        <v>52</v>
+      </c>
+      <c r="C5" s="16" t="s">
+        <v>44</v>
       </c>
       <c r="H5" s="11" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="I5" s="11"/>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A6" s="18" t="s">
-        <v>40</v>
-      </c>
-      <c r="C6" s="18" t="s">
-        <v>49</v>
+      <c r="A6" s="16" t="s">
+        <v>36</v>
+      </c>
+      <c r="C6" s="16" t="s">
+        <v>45</v>
       </c>
       <c r="H6" s="11" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="I6" s="11"/>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A7" s="18" t="s">
-        <v>41</v>
-      </c>
-      <c r="C7" s="18" t="s">
-        <v>50</v>
-      </c>
-      <c r="H7" s="18"/>
+      <c r="A7" s="16" t="s">
+        <v>37</v>
+      </c>
+      <c r="C7" s="16" t="s">
+        <v>46</v>
+      </c>
+      <c r="H7" s="16"/>
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A8" s="11" t="s">
-        <v>56</v>
-      </c>
-      <c r="C8" s="18" t="s">
-        <v>36</v>
+        <v>52</v>
+      </c>
+      <c r="C8" s="16" t="s">
+        <v>32</v>
       </c>
     </row>
   </sheetData>
